--- a/data/trans_orig/IP37-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34433</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58034</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83975</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102338</t>
+          <t>101284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>36163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>32405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56936</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>57399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>72638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104791</t>
+          <t>103475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125491</t>
+          <t>125600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64899</t>
+          <t>64790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85599</t>
+          <t>86915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35153</t>
+          <t>35670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47823</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>92591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57876</t>
+          <t>57909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>42056</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>57011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>82965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102318</t>
+          <t>101613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64611</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>171440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197088</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214065</t>
+          <t>215929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365387</t>
+          <t>366403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404206</t>
+          <t>403945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102878</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>128910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214225</t>
+          <t>214486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253044</t>
+          <t>252028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>57253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74151</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121588</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141228</t>
+          <t>140844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32634</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33409</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>53795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84700</t>
+          <t>84282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98624</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>92659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107581</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182481</t>
+          <t>182667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203114</t>
+          <t>203247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>40599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61365</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66277</t>
+          <t>66245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>54916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68366</t>
+          <t>68838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111798</t>
+          <t>112514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131477</t>
+          <t>131685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43785</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63464</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89361</t>
+          <t>89584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66185</t>
+          <t>66157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81966</t>
+          <t>82044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145897</t>
+          <t>145715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168260</t>
+          <t>166773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>31966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>43272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64148</t>
+          <t>64330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284784</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312239</t>
+          <t>312540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290227</t>
+          <t>287798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317646</t>
+          <t>318138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580782</t>
+          <t>582699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>623064</t>
+          <t>623538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97047</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124466</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180726</t>
+          <t>180252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223008</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>49151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62384</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52766</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>105818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125330</t>
+          <t>126188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81858</t>
+          <t>82414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95232</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>74959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91238</t>
+          <t>91335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161782</t>
+          <t>161066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182476</t>
+          <t>182803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69977</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48043</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60685</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>51173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64414</t>
+          <t>63914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103462</t>
+          <t>103453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122202</t>
+          <t>121575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>69399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82640</t>
+          <t>83086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59605</t>
+          <t>58712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71729</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132791</t>
+          <t>131472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152452</t>
+          <t>151145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>262856</t>
+          <t>263178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288726</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255559</t>
+          <t>254604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283291</t>
+          <t>282717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525049</t>
+          <t>526669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>563719</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83551</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165452</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43253</t>
+          <t>43476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>40945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54299</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>47325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61986</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91649</t>
+          <t>91529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113131</t>
+          <t>113288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53375</t>
+          <t>53495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>83463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39160</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>51950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102708</t>
+          <t>101726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134729</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55442</t>
+          <t>56424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>46564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61730</t>
+          <t>61466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79772</t>
+          <t>79238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51067</t>
+          <t>51331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162495</t>
+          <t>163670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>205255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162932</t>
+          <t>164795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192773</t>
+          <t>193078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338564</t>
+          <t>339051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390416</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123652</t>
+          <t>125858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175504</t>
+          <t>175017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP37-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51430</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43961</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57331</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>41942</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34488</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47858</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35032</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48945</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51430</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>44772</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>57532</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>66,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>84016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101284</t>
+          <t>103017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19846</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28709</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36163</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21706</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35619</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25747</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19645</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32405</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77177</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77177</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77177</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>77177</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>77177</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>77177</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65410</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57509</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73069</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>49845</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>42837</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57049</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42715</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56965</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>56,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>48,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65410</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>57399</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72638</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103475</t>
+          <t>104128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125600</t>
+          <t>124992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36166</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28507</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44067</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>38969</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31765</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45977</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31849</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>46099</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>43,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36166</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28938</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>44177</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101576</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101576</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101576</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101576</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101576</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101576</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48849</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41880</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35670</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35855</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47583</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42502</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36637</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48652</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75751</t>
+          <t>74834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92591</t>
+          <t>92654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25223</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18876</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31503</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24054</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17809</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30264</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18351</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30079</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25223</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19073</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31088</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41069</t>
+          <t>41006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57909</t>
+          <t>58826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41657</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34746</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48772</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>49,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>50634</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42056</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43665</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57241</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>66,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>41657</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34954</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48111</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82965</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101613</t>
+          <t>102101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28808</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21693</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35719</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>50,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>25455</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19078</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34033</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18848</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32424</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>33,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28808</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22354</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35511</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44941</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>64401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>186230</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>213697</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>171440</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>198509</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>171439</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>56,86%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>188033</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>215929</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>59,33%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>366403</t>
+          <t>364768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403945</t>
+          <t>404199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115944</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>103246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130713</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>117187</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102979</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>130048</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101635</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>130049</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,87%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>43,14%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115944</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101014</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128910</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214486</t>
+          <t>214232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252028</t>
+          <t>253663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67562</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74154</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>64648</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57253</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70672</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57896</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70847</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>67562</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60345</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>73971</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120842</t>
+          <t>122182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140844</t>
+          <t>141093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18234</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31650</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17601</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11577</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24996</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24353</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24826</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18417</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32043</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53795</t>
+          <t>52455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>92388</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>92388</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>92388</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82249</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>82249</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>82249</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>92388</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>92388</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>92388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100418</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>92635</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>106883</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91857</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>84282</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>98901</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>84948</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>98411</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>100418</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>92659</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>107506</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>182667</t>
+          <t>182166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203247</t>
+          <t>202710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25530</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19065</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33313</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>26041</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18997</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33616</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19487</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32950</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>25530</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18442</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33289</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>41136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>125948</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>125948</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>125948</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>117898</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>117898</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>117898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>125948</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>125948</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>125948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61785</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54196</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68783</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>60542</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66245</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>53005</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66248</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>61785</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>54916</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>68838</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112514</t>
+          <t>111477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131685</t>
+          <t>131507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30828</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23830</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38417</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22107</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16404</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28619</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16401</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29644</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30828</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37697</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>63785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>92613</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>92613</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>92613</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>82649</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>82649</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>82649</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>92613</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>92613</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>92613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74458</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>66632</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82677</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>82508</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>74334</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>89584</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>75105</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>89661</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>77,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>74458</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>66157</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82044</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145715</t>
+          <t>144953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166773</t>
+          <t>166783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29287</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21068</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37113</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23792</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16716</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31966</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31195</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>22,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29287</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21701</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37588</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64330</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>106300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>106300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>106300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>289252</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>319160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>284619</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>312540</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>285815</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>312603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>287798</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>318138</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>582699</t>
+          <t>583210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>623538</t>
+          <t>621768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>110471</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>125441</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>89541</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76557</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>104478</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76494</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>103282</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110471</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>96555</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126895</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180252</t>
+          <t>182022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>221091</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>559</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>60169</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52390</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>74,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>56029</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49151</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>62331</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49665</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>62699</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60169</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53167</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66009</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105818</t>
+          <t>106450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126188</t>
+          <t>125042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20559</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14543</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28338</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21441</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15139</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28319</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14771</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27805</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20559</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14719</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27561</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80728</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80728</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80728</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>77470</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>77470</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>77470</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80728</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80728</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80728</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83288</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74774</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91500</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89556</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82414</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>95323</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>83029</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>95538</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>81,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>86,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83288</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>74959</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>91335</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161066</t>
+          <t>161646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182803</t>
+          <t>182828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38511</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30299</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47025</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20404</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14637</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27546</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26931</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>18,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38511</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30464</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>46840</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48956</t>
+          <t>48931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>121799</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>121799</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>121799</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>109960</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>109960</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>109960</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>121799</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>121799</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>58604</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51961</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64976</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>54686</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47431</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60473</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47788</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>60356</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58604</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51173</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>63914</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>104314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121575</t>
+          <t>122227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20950</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14578</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27593</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>23188</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17401</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30443</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17518</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30086</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20950</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15640</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28381</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>35201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>53114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79554</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79554</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79554</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>77874</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>77874</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>77874</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79554</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79554</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66415</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58689</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71824</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>76542</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69399</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83086</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>68996</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>83043</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>78,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>66415</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>58712</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72248</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>78,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131472</t>
+          <t>132219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151145</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18347</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26073</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20482</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13938</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27625</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13981</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28028</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>21,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18347</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12514</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>26050</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50314</t>
+          <t>49567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>84762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>84762</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>84762</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>97024</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>97024</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>97024</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>84762</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>84762</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>84762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>254378</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>281816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>263178</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>289108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>262174</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>289089</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>254604</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>282717</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>69,4%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>802</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>526669</t>
+          <t>525292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>564503</t>
+          <t>563262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98366</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>85026</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112464</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>85515</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73221</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>99151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>73240</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>100155</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>98366</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>84125</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112238</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>165909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>203879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31064</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24412</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35215</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32463</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26475</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37334</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>64742</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61657</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78759</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9631</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16283</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17223</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12352</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>36438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50837</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42361</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57491</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>48068</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40945</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54779</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54862</t>
+          <t>42829</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>35678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>102930</t>
+          <t>93666</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91529</t>
+          <t>82170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113288</t>
+          <t>103732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24484</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32960</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16254</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9543</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23377</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53495</t>
+          <t>51848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>75321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>75321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>75321</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64322</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64322</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>64322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80702</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80702</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80702</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>145024</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42305</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35485</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>69258</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56562</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83463</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>78928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101726</t>
+          <t>70088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136339</t>
+          <t>88340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17707</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24527</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>23804</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9599</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36500</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42655</t>
+          <t>41925</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>50765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>60012</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>60012</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>60012</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>93062</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>93062</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>93062</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>158150</t>
+          <t>120853</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>158150</t>
+          <t>120853</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158150</t>
+          <t>120853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38251</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32233</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44141</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30668</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24433</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36307</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>60,64%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40617</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33043</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46564</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71285</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61466</t>
+          <t>60919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79238</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>40773</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51331</t>
+          <t>49660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59044</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59044</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59044</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>50574</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>50574</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>50574</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62223</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62223</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62223</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>150383</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>175572</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>163670</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>205255</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>131478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>155723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339051</t>
+          <t>289848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388210</t>
+          <t>326240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>59500</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>84689</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>77187</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93974</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>78410</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91629</t>
+          <t>91619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>153647</t>
+          <t>151026</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125858</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175017</t>
+          <t>168321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
